--- a/untranslated/downloads/data-excel/2.a.1.xlsx
+++ b/untranslated/downloads/data-excel/2.a.1.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE5F3A89-4050-4A9C-9838-F380C40172BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15" yWindow="5940" windowWidth="28830" windowHeight="6000"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -115,25 +116,21 @@
       <charset val="204"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <sz val="9"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -182,43 +179,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -228,21 +212,20 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 6" xfId="2"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 6" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -258,9 +241,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -298,9 +281,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -335,7 +318,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -370,7 +353,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -543,7 +526,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -551,176 +534,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:20" ht="19.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="5"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
+    <row r="2" spans="1:20" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="9"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:20" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D3" s="5">
         <v>2007</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E3" s="5">
         <v>2008</v>
       </c>
-      <c r="F3" s="8">
+      <c r="F3" s="5">
         <v>2009</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="5">
         <v>2010</v>
       </c>
-      <c r="H3" s="8">
+      <c r="H3" s="5">
         <v>2011</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="5">
         <v>2012</v>
       </c>
-      <c r="J3" s="9">
+      <c r="J3" s="5">
         <v>2013</v>
       </c>
-      <c r="K3" s="9">
+      <c r="K3" s="5">
         <v>2014</v>
       </c>
-      <c r="L3" s="8">
+      <c r="L3" s="5">
         <v>2015</v>
       </c>
-      <c r="M3" s="9">
+      <c r="M3" s="5">
         <v>2016</v>
       </c>
-      <c r="N3" s="9">
+      <c r="N3" s="5">
         <v>2017</v>
       </c>
-      <c r="O3" s="12">
+      <c r="O3" s="8">
         <v>2018</v>
       </c>
-      <c r="P3" s="12">
+      <c r="P3" s="8">
         <v>2019</v>
       </c>
-      <c r="Q3" s="12">
+      <c r="Q3" s="8">
         <v>2020</v>
       </c>
-      <c r="R3" s="12">
+      <c r="R3" s="8">
         <v>2021</v>
       </c>
-      <c r="S3" s="12">
+      <c r="S3" s="8">
         <v>2022</v>
       </c>
-      <c r="T3" s="12">
+      <c r="T3" s="8">
         <v>2023</v>
       </c>
     </row>
-    <row r="4" spans="1:20" s="20" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="13">
         <v>8.9219330855018583E-2</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="13">
         <v>6.3829787234042548E-2</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="13">
         <v>7.9787234042553182E-2</v>
       </c>
-      <c r="G4" s="18">
+      <c r="G4" s="13">
         <v>6.8571428571428575E-2</v>
       </c>
-      <c r="H4" s="18">
+      <c r="H4" s="13">
         <v>6.0240963855421679E-2</v>
       </c>
-      <c r="I4" s="18">
+      <c r="I4" s="13">
         <v>4.8192771084337345E-2</v>
       </c>
-      <c r="J4" s="18">
+      <c r="J4" s="13">
         <v>6.8493150684931503E-2</v>
       </c>
-      <c r="K4" s="18">
+      <c r="K4" s="13">
         <v>6.1224489795918373E-2</v>
       </c>
-      <c r="L4" s="18">
+      <c r="L4" s="13">
         <v>7.8571428571428584E-2</v>
       </c>
-      <c r="M4" s="18">
+      <c r="M4" s="13">
         <v>7.8125E-2</v>
       </c>
-      <c r="N4" s="18">
+      <c r="N4" s="13">
         <v>7.2000000000000008E-2</v>
       </c>
-      <c r="O4" s="18">
+      <c r="O4" s="13">
         <v>9.401709401709403E-2</v>
       </c>
-      <c r="P4" s="18">
+      <c r="P4" s="13">
         <v>9.130340807234763E-2</v>
       </c>
-      <c r="Q4" s="18">
+      <c r="Q4" s="13">
         <v>7.4862480994528399E-2</v>
       </c>
-      <c r="R4" s="19">
+      <c r="R4" s="14">
         <v>6.4467421337540437E-2</v>
       </c>
-      <c r="S4" s="19">
+      <c r="S4" s="14">
         <v>7.1025550219041236E-2</v>
       </c>
-      <c r="T4" s="19">
+      <c r="T4" s="14">
         <v>0.1060493949263058</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="11"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="B6" s="11"/>
+      <c r="B6" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
